--- a/tools/excel/3xlsx/animal.xlsx
+++ b/tools/excel/3xlsx/animal.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SceneObj/Box/ammo_box_01</t>
+          <t>Animals/Goose</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -620,7 +620,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SceneObj/Box/ammo_box_02</t>
+          <t>Animals/Rabbit_Brown</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -644,7 +644,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SceneObj/Box/ammo_box_03</t>
+          <t>Animals/Boar</t>
         </is>
       </c>
       <c r="D9" t="n">

--- a/tools/excel/3xlsx/animal.xlsx
+++ b/tools/excel/3xlsx/animal.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,7 +603,7 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>野兔</t>
+          <t>兔子</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -627,7 +627,7 @@
         <v>150</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -639,7 +639,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>野猪</t>
+          <t>猪</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -651,12 +651,500 @@
         <v>300</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>熊</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Animals/Bear_Grizzly</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>600</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>牛</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Animals/Cow_Horns_Brown</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>280</v>
+      </c>
+      <c r="E11" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>骆驼</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Animals/Camel_Dromedary</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>400</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>奶牛</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Animals/Cow_White</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>260</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>鳄鱼</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Animals/Crocodile</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>鹿</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Animals/Deer</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>300</v>
+      </c>
+      <c r="E15" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>大象</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Animals/Elephant_Male</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>长颈鹿</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Animals/Giraffe</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>700</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>山羊</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Animals/Goat</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>180</v>
+      </c>
+      <c r="E18" t="n">
+        <v>35</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>鸡</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Animals/Hen</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>河马</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Animals/Hippo</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>600</v>
+      </c>
+      <c r="E20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>马</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Animals/Horse_Brown</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>320</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>狮子</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Animals/Lion_Male</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>700</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>麋鹿</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Animals/Reindeer</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>350</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>犀牛</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Animals/Rhino</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>800</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>绵羊</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Animals/Sheep_Wool</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>180</v>
+      </c>
+      <c r="E25" t="n">
+        <v>35</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>老虎</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Animals/Tiger</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>700</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>狼</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Animals/Wolf</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>350</v>
+      </c>
+      <c r="E27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>斑马</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Animals/Zebra</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>400</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
